--- a/data/trans_bre/P14B23-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Edad-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,2</t>
+          <t>-0,31; 1,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,02</t>
+          <t>0,2; 3,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,97</t>
+          <t>-2,09; 5,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,36; —</t>
+          <t>-46,06; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 907,5</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,76</t>
+          <t>0,77; 3,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,92</t>
+          <t>-0,14; 1,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,42</t>
+          <t>1,2; 5,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,21; 1072,15</t>
+          <t>34,4; 1178,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,69; —</t>
+          <t>-90,6; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,49; 2392,91</t>
+          <t>35,84; 1686,31</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,41</t>
+          <t>0,39; 5,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,02</t>
+          <t>0,62; 4,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,38</t>
+          <t>-2,11; 2,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 210,49</t>
+          <t>1,75; 206,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 396,63</t>
+          <t>20,37; 451,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 81,3</t>
+          <t>-36,82; 103,12</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,95</t>
+          <t>2,72; 7,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,45</t>
+          <t>2,52; 7,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,33</t>
+          <t>1,56; 7,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,89; 490,7</t>
+          <t>56,78; 426,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,63; 344,95</t>
+          <t>55,08; 362,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,29; 400,92</t>
+          <t>28,09; 399,44</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 13,09</t>
+          <t>5,33; 13,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,21</t>
+          <t>4,19; 10,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,72</t>
+          <t>3,23; 8,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,92; 427,25</t>
+          <t>84,09; 452,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,3; 424,19</t>
+          <t>82,4; 471,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,72; 208,29</t>
+          <t>42,1; 198,61</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,94</t>
+          <t>6,58; 15,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 13,97</t>
+          <t>7,15; 14,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 8,06</t>
+          <t>-0,85; 8,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113,84; 767,88</t>
+          <t>98,31; 769,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>270,8; 3941,55</t>
+          <t>251,39; 3801,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 319,95</t>
+          <t>-21,83; 331,71</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 16,12</t>
+          <t>6,68; 15,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 12,09</t>
+          <t>3,35; 12,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,68</t>
+          <t>2,94; 8,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94,17; 807,69</t>
+          <t>76,5; 763,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,9; 517,57</t>
+          <t>52,99; 521,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,43; 241,8</t>
+          <t>44,61; 265,95</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,65</t>
+          <t>4,44; 6,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1204,22 +1204,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,74</t>
+          <t>2,09; 4,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149,08; 326,82</t>
+          <t>149,52; 324,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>158,33; 353,73</t>
+          <t>156,58; 344,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,83; 154,67</t>
+          <t>51,33; 159,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P14B23-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,38</t>
+          <t>-0,18; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,99</t>
+          <t>0,23; 3,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,58</t>
+          <t>-2,1; 4,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,06; —</t>
+          <t>-32,39; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,38; 574,65</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>364,9%</t>
+          <t>207,4%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,78</t>
+          <t>0,8; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,88</t>
+          <t>-0,07; 1,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,47</t>
+          <t>0,77; 5,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,4; 1178,0</t>
+          <t>43,12; 1182,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,6; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,84; 1686,31</t>
+          <t>1,22; 868,91</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,5</t>
+          <t>0,96; 5,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,25</t>
+          <t>0,56; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,8</t>
+          <t>-0,78; 3,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 206,6</t>
+          <t>13,15; 238,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,37; 451,45</t>
+          <t>16,69; 390,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 103,12</t>
+          <t>-15,2; 138,54</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>116,7%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,67</t>
+          <t>2,53; 7,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,75</t>
+          <t>2,19; 7,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,58</t>
+          <t>0,97; 5,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,78; 426,73</t>
+          <t>60,15; 473,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,08; 362,18</t>
+          <t>49,18; 333,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,09; 399,44</t>
+          <t>13,93; 156,63</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>104,06%</t>
+          <t>116,03%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,17</t>
+          <t>5,34; 12,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,92</t>
+          <t>4,27; 11,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,65</t>
+          <t>3,83; 8,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,09; 452,29</t>
+          <t>88,23; 426,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,4; 471,66</t>
+          <t>75,83; 438,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,1; 198,61</t>
+          <t>48,85; 201,66</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>123,85%</t>
+          <t>260,81%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,56</t>
+          <t>6,61; 15,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,04</t>
+          <t>7,1; 14,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,26</t>
+          <t>4,98; 10,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98,31; 769,14</t>
+          <t>87,64; 821,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>251,39; 3801,46</t>
+          <t>311,54; 4123,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 331,71</t>
+          <t>109,93; 532,44</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>115,28%</t>
+          <t>108,88%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,7</t>
+          <t>7,16; 15,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 12,26</t>
+          <t>3,5; 11,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,72</t>
+          <t>2,48; 8,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76,5; 763,45</t>
+          <t>94,83; 813,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,99; 521,03</t>
+          <t>60,34; 473,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,61; 265,95</t>
+          <t>32,7; 244,9</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>109,27%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,66</t>
+          <t>4,48; 6,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,73</t>
+          <t>3,79; 5,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,79</t>
+          <t>3,1; 5,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149,52; 324,38</t>
+          <t>149,19; 317,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>156,58; 344,64</t>
+          <t>164,33; 345,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,33; 159,68</t>
+          <t>69,2; 156,78</t>
         </is>
       </c>
     </row>
